--- a/evaluation/OLS_Regression_Feature_Analysis_accuracy_metric_based.xlsx
+++ b/evaluation/OLS_Regression_Feature_Analysis_accuracy_metric_based.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,14 +458,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Number of Users Rating per User</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41699304620.0976</v>
+        <v>399.8443564399277</v>
       </c>
       <c r="C2" t="n">
-        <v>0.80416878209806</v>
+        <v>0.4580430155556624</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
@@ -477,16 +477,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dataset_ml1m</t>
+          <t>Shape Rating per User</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27507447966.72452</v>
+        <v>92.26060062580088</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8041687820976956</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>0.02282980754060017</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -496,14 +500,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dataset_BX</t>
+          <t>Number of Ratings Shape</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27507447966.61755</v>
+        <v>30.31654798222536</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8041687820984377</v>
+        <v>0.6705920216474952</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
@@ -515,16 +519,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Model Name_FOCF</t>
+          <t>Rating per Item Standart Deviation of Rating</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18221771153.32562</v>
+        <v>18.94238772442704</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8041687820964875</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>0.002317225155644302</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -534,16 +542,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Model Name_PFCN_MLP</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18221771153.15858</v>
+        <v>16.06577116656162</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8041687820982473</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>0.01025740535309007</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -553,14 +565,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Model Name_NFCF</t>
+          <t>Number of Users</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18221771153.04324</v>
+        <v>12.12243409459204</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8041687820994616</v>
+        <v>0.3676945149331403</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
@@ -572,20 +584,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Differential Fairness of sensitive attribute</t>
+          <t>Number of Users Dataset_BX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2712765201384789</v>
+        <v>11.93804591839615</v>
       </c>
       <c r="C8" t="n">
-        <v>5.261269853731772e-14</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>0.3122879956288652</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -595,18 +603,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gini Item</t>
+          <t>Shape Dataset_ml1m</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2359360654501033</v>
+        <v>11.80714815024644</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001676018324917555</v>
+        <v>0.03124843996802142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>*</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -618,20 +626,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rating per Item</t>
+          <t>Number of Users Sensitive Feature_Age</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1648450119694923</v>
+        <v>10.64078041242643</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001356877968573941</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
+        <v>0.3695150564232221</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -641,20 +645,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KS Statistic of sensitive attribute</t>
+          <t>Gini User</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.150180630675426</v>
+        <v>10.41770456413817</v>
       </c>
       <c r="C11" t="n">
-        <v>2.407028775202049e-09</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>0.0859426383174311</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -664,14 +664,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Number of Users</t>
+          <t>Standart Deviation of Rating Dataset_BX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05282992919754335</v>
+        <v>8.753820713808011</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2929811891537768</v>
+        <v>0.2204441184387311</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
@@ -683,14 +683,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Generalized Cross Entropy</t>
+          <t>Generalized Cross Entropy Mean Rating</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0472986977370351</v>
+        <v>8.634567427393629</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1978775221567238</v>
+        <v>0.06985077355819103</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
@@ -702,14 +702,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Overestimation Unfairness of sensitive attribute</t>
+          <t>Number of Users Mean Rating</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04497739691499196</v>
+        <v>8.414545341967068</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2553913015311434</v>
+        <v>0.2677153813774127</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
@@ -721,16 +721,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Skewness of Popularity Bias</t>
+          <t>Shape Sensitive Feature_Age</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03162248074623818</v>
+        <v>7.997511822857874</v>
       </c>
       <c r="C15" t="n">
-        <v>0.274097834775876</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>0.009598469133145431</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -740,14 +744,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mean Rating</t>
+          <t>Density Mean Rating</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02875434477238261</v>
+        <v>7.889640487517248</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8603899851831217</v>
+        <v>0.5709908388037528</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
@@ -759,16 +763,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Skewness of Long Tail Items</t>
+          <t>Shape Sensitive Feature_Gender</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.00606643925008632</v>
+        <v>7.777101436212132</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8296775003742043</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>0.01096069218079666</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -778,14 +786,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rating per User</t>
+          <t>Density Gini User</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.005336387379640893</v>
+        <v>7.581325305737177</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8663810368339108</v>
+        <v>0.1451608090993878</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
@@ -797,16 +805,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Number of Ratings</t>
+          <t>Shape Dataset_BX</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01467150863390797</v>
+        <v>7.352838225502636</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8483598331143329</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>0.002511651426751167</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -816,14 +828,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Number of Items</t>
+          <t>Density Gini Item</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.01991315284898296</v>
+        <v>7.335302421828291</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6702311735250499</v>
+        <v>0.09768950443808676</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
@@ -835,14 +847,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Standart Deviation of Rating</t>
+          <t>Mean Rating Standart Deviation of Rating</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.02295081127665986</v>
+        <v>7.242589985355742</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7866222621882895</v>
+        <v>0.4802254614978912</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
@@ -854,14 +866,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Skewness of Popularity Bias Standart Deviation of Rating</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03829371447221433</v>
+        <v>6.465641471943623</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4139714240199367</v>
+        <v>0.3188941428891789</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
@@ -873,14 +885,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Difference between Sensitive Attribute Percentage</t>
+          <t>Gini User Dataset_ml1m</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06598469430278966</v>
+        <v>5.788524467534955</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3268437027493291</v>
+        <v>0.3154923095816613</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
@@ -892,20 +904,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gini User</t>
+          <t>Number of Items Gini User</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.09557520556642594</v>
+        <v>5.770907345906581</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0249688886881168</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.1278821748260449</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -915,20 +923,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Value Unfairness of sensitive attribute</t>
+          <t>Number of Users Gini User</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1202566784425576</v>
+        <v>5.678489447260066</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0002595508447702987</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>0.3962225476316521</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>hit@5</t>
@@ -938,14 +942,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Shape Model Name_FOCF</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1808324811066227</v>
+        <v>5.504429388251573</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002544954583323742</v>
+        <v>0.007238068894748389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -961,14 +965,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Age</t>
+          <t>Rating per Item Gini User</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-87428523739.9176</v>
+        <v>5.182200519576659</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8041687820981194</v>
+        <v>0.3627944250193734</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
@@ -980,17 +984,6316 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Shape Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5.146667268347141</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.01187193643456258</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shape Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5.123516602225662</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.01247868632334039</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Rating per Item Gini Item</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5.099138794721019</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1781097415663335</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Mean Rating</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4.687385047211196</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.2063176795553733</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Density Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4.459254244034968</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.5531362535548878</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Number of Items Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4.428774520111022</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.06736616614666574</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Number of Users Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4.009279813751654</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.3627138441077034</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Number of Users Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3.982648884223261</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.3663229522195862</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Number of Users Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3.905818990330226</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.3762232119955013</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Number of Users Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3.706783799653227</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.3577708800231756</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Density Rating per User</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.702207443443418</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.02728989047200525</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Rating per User Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3.642878427932988</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.02696369768351226</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Number of Ratings Mean Rating</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3.637864861762309</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7209078183447477</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3.545026571755474</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.2134077547038131</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Rating per User</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.340863445149583</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.264417738260082</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.12132891149701</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5414462182670612</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.92628777351601</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.3837563298141035</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gini Item Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.924346993195669</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.5061825016772619</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2.656747091849537</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.5819890495293882</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Gini User</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.494238210481956</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.00299902316076732</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Mean Rating</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2.383531684625579</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.6997752577667775</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rating per User Rating per Item</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2.379897289881779</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.5232213052454927</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Difference between Sensitive Attribute Percentage Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2.341769416839761</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.5782295163434158</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gini Item</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2.146844745375742</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7292296474507626</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gini User Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2.078164528303417</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.06864564723172217</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Number of Users Density</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.042734189082474</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.4804029696773739</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Rating per Item Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1.986264163940272</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0368940178941569</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Number of Users</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.956577891976983</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.02090245313882206</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Gini User</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1.94688302551665</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.1792971829325774</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gini User Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.91911497329105</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.4909227661508047</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1.816493765423537</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7562538471514262</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Rating per User Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.747210998149733</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.1802487386523028</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Number of Users Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1.722325593957022</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.03217488513408198</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.668238255162647</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.2423941338116234</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Mean Rating Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1.648330140248351</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.847839725749839</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Difference between Sensitive Attribute Percentage Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1.607035376560207</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5508316835441067</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Rating per User Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1.497909906076222</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5749779237264324</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.490864642402745</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.500441134101498</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Gini Item Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1.449683234878278</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.4271238337290402</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1.412387048964896</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.3084883795609484</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Number of Users Gini Item</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1.411521360697577</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.6430410574086597</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Rating per Item</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1.354924927934813</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.09345293251325627</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Number of Items Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1.34346075077677</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.03850613667716873</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Number of Ratings</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1.328455275904215</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.01283435031974854</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Gini User Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1.315541176647024</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.05227951329443871</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Mean Rating Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1.28709211113164</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.7926263331898187</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Model Name_FOCF Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.280800435086223</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.5270526608877538</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1.258242342182244</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.5281261260906993</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Number of Users Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1.256800244861056</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.1270874874262668</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Gini Item Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1.242961225198592</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.2879856130476609</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Rating per User Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1.197029306038829</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.1760464303468742</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Gini User Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1.16431749085759</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.1099124230611849</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Difference between Sensitive Attribute Percentage Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1.142620644804827</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.6194879041434338</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Sensitive Feature_Gender</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>-87428523739.94202</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.8041687820980659</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
+      <c r="B81" t="n">
+        <v>1.118026528188724</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.5726557425339632</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sensitive Feature_Gender Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1.118026519467652</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.5726557441256319</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Rating per User Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1.112150733868025</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.3963670772031608</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Mean Rating</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1.097459295606973</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.6374943272386728</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Rating per User Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1.047948225366414</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.2229263111675468</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Difference between Sensitive Attribute Percentage Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1.013134403453136</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.5129713913682954</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Gini Item Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1.011186528404196</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.8219424502061293</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Value Unfairness of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1.003926562814951</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.1190259377873217</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gini Item Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.9944591039327477</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.3882947022978666</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Shape Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.9816616712254319</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.3810196393881555</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.980915344825493</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.4963463753825058</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Rating per Item Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.9388830982976595</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.02724177539179513</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.9109886650240981</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.5196602657654685</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Gini User Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.9074173737736935</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.3886083633183895</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Gini User</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.9039899417265993</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.5181962192783363</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.9002389707608083</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.5307030801502396</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Difference between Sensitive Attribute Percentage Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.8682339204989227</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.5758396234677357</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.8013765442895411</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.2084713054483136</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Number of Items Number of Ratings</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.7973456399266647</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.6108518350889915</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.7863585601748566</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.5192661711475692</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.7804107377936966</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.4154942058567654</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Number of Items</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.7583531059568922</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.2441781573059089</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute KS Statistic of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.7384243269243547</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.0249714178471802</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Gini Item</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0.7369058159949528</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.3153617378320721</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.7327227418562711</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.226138272683601</v>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Difference between Sensitive Attribute Percentage Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.7066589388023126</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.656423793698929</v>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Number of Users</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.7000516524950049</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.001169642510137915</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sensitive Feature_Age Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.6984672285042208</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.8664361165950423</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Mean Rating Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.693599021160086</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.7586839730263859</v>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Density</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0.6526745666633711</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.07837146744169007</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Shape</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.6349795168980816</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.0594867851035649</v>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.6329598297859353</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.6283737485283081</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Model Name_FOCF Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.6255055220455811</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.4052692477762441</v>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Rating per User Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.6143842025343967</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.4730949338810783</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.5996120827084797</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.5281375533219621</v>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Number of Users Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0.5990095268639906</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.3624872050135581</v>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Number of Items</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.5975732352513485</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.1730808317618268</v>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.5904735032955448</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.5707937353554097</v>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0.5665908813909676</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.3543710906935966</v>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0.5649345135331867</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.8335838744384118</v>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Number of Items Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0.5282727878859154</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.2450225900897566</v>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Rating per User</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0.520938414396764</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3411694250414974</v>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.5118811873404745</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.5923555590148508</v>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Difference between Sensitive Attribute Percentage Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4981715271067734</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.7871596185495749</v>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.4945132477226241</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.5078885339814426</v>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.4933261324517132</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.6022422600837849</v>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.4883633046062084</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5625786131906949</v>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Shape</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0.4286628061068174</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.4121536586290306</v>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Number of Ratings Rating per Item</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.4261550080978396</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.5668051082132123</v>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.4225143740827617</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.5614576727031911</v>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Gini Item Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.4148082573168417</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.9204777066857581</v>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Rating per Item</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.4023185002939489</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.5965971677760546</v>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3920926663910689</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.6090533397283999</v>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Number of Users Number of Items</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3863610323607194</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.8624540242745359</v>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3807993599146405</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.9120061620220372</v>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Rating per User Gini User</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3628154450012309</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.844595760615554</v>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0.3627910519387778</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.795459792371392</v>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Gini User Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3625889460367028</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.6376689950040513</v>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Model Name_PFCN_MLP Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3418946169082995</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8603715960250528</v>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Number of Items</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3387332681554954</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.1302481488305902</v>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3251545307309057</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.4974575139298557</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Number of Items Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3203692141030885</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9770872910481112</v>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3083765310472567</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7711835121952972</v>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Model Name_PFCN_MLP Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0.3034271739364491</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.648053422486244</v>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0.2979627850616207</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.8626467780680083</v>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Rating per User Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0.2859534195027685</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.723648665617787</v>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Generalized Cross Entropy</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.2762984063382556</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.07100952053330363</v>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.2721413663631364</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.3544586987389976</v>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.2689297650006388</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.6429245914228288</v>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0.2672607378633214</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.6307131858433321</v>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.249255729147026</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.03831953209066778</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Rating per User Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0.2427125041532926</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.6329767267775255</v>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0.2379147728305111</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.8829458340752826</v>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Rating per Item</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0.2344516032959131</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.2266831734547274</v>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Number of Items Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.2171495187392366</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.7296902164532562</v>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Generalized Cross Entropy</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0.2142376075449788</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.6960781377765186</v>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Mean Rating Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0.2054716005558923</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.9466538962270675</v>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0.1956710844267482</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.9530605118470503</v>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Model Name_NFCF Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.1937986965020624</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.9219267509164952</v>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Model Name_NFCF Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0.1890938237434954</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.7825424556904892</v>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Number of Ratings</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.179062360372186</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.8769816200596401</v>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Rating per Item Mean Rating</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.1568100426222938</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.9879434228251596</v>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.1548281020062646</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.09515675806693041</v>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Rating per User</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0.1540618615664702</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.8286950040223189</v>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Generalized Cross Entropy</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0.1502566945453696</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.597610146485513</v>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Rating per User</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0.134796915818592</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.7241061409925538</v>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Number of Users</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0.1179427823635848</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.5745380933461988</v>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Rating per User</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0.1083436864303612</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.5914380650326778</v>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0.09184192456422315</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.5974869051122661</v>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Density Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0.07976398870494505</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.8423494083588353</v>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0.07192486031464584</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.9165834951723227</v>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0.05345008081733472</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.9330068822161731</v>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0.04401443702699126</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.9968130681265213</v>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Number of Items Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0.03685678708566642</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.9706788129129169</v>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0.02491675331926935</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.9662743832758852</v>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0.009694560144181061</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.9790266865801757</v>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Model Name_FOCF Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0.007454307184277087</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.9913059533207987</v>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0.000444435292320966</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.9996600506440256</v>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Model Name_FOCF Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Model Name_FOCF Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Model Name_NFCF Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sensitive Feature_Age Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sensitive Feature_Gender Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Dataset_BX Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Number of Ratings</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>-0.008365639626226939</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.9879795283709413</v>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Number of Users Shape</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>-0.02066624526227279</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.97699005598058</v>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>-0.03694407572592845</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.9692521557395322</v>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Number of Users Number of Ratings</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>-0.04844490065664153</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.935142792308256</v>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>-0.05982523996223671</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.8317219239463178</v>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>-0.06149692932944673</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.8825573825823401</v>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Generalized Cross Entropy</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>-0.06842895518638065</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.8031535892750781</v>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Density</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>-0.08006771044952343</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.9213550698650189</v>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>-0.08825306862599169</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.9370333226311797</v>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>-0.09019395171406308</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.8412200047700392</v>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>-0.09158655525021064</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.9860649591023631</v>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Shape</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>-0.09820988828572164</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.8927749170385313</v>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>-0.112658569125243</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.6220367679301545</v>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Number of Items Gini Item</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>-0.1174759478766201</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.9471939642281695</v>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Number of Users Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>-0.1188390758041358</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.9828283219912447</v>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>-0.1224768338353592</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.9310863266437666</v>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Number of Items</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>-0.1253769641901211</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.6918029245885573</v>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>-0.1333531558612664</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.6061647039165167</v>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Gini Item Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>-0.1340559687007752</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.9393269014336518</v>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Rating per Item</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>-0.1391967543379519</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.773997060614475</v>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Density Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>-0.151593714519028</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.9029207006473134</v>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>-0.1645481537951152</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.8257052446280121</v>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Number of Ratings Rating per User</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>-0.1817636254015044</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.8106287416808418</v>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>-0.1916078639342287</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.6989818917493886</v>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Mean Rating</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>-0.1968421238351619</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.9601637128765395</v>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Rating per User Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>-0.2436221264918855</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.3886764071335347</v>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Rating per User</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>-0.2455731160847876</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.725022007576362</v>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Number of Users</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>-0.2603363402858843</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.4987787774613434</v>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>-0.2666118013073397</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.646711621384618</v>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>-0.3323574644147336</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.3342007424157515</v>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Number of Ratings</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>-0.3365188370545909</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.1370910378449012</v>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Shape</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>-0.3461942176989753</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.02717899267205021</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>-0.3490356808283133</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.7676803083963751</v>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Overestimation Unfairness of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>-0.3746455395343069</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.6235906234797196</v>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Gini Item Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>-0.3904187583703655</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.7036736409571972</v>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Model Name_PFCN_MLP Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>-0.3916802430772322</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.5129188097238125</v>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-0.4158276474176139</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.3084869549232178</v>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute KS Statistic of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>-0.4265367827038397</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.1709297459718683</v>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Model Name_PFCN_MLP Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>-0.4301476848270873</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.7423812792598199</v>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Number of Items Rating per User</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>-0.4367352343035336</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.5081804699753703</v>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Mean Rating Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-0.4678735068643727</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.8228754868081396</v>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>-0.4682686076120091</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.6716537038121519</v>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Mean Rating Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>-0.4834089865775395</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.886849570460376</v>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Mean Rating Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>-0.5036629017978225</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.8257301392367331</v>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>-0.5058929832602516</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.3161421680828304</v>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Density</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>-0.5241403370147859</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.5282867905048623</v>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>-0.5294987603552554</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.2886421154931598</v>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Density Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>-0.5340871340742461</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.735038812344862</v>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Model Name_NFCF Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>-0.5381295024307542</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.3984358545817205</v>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Number of Items Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>-0.5407371370867586</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.5675547953345952</v>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Model Name_NFCF Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>-0.5428343752606595</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.678489328319865</v>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Mean Rating</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>-0.5496313487370166</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.8819040921963482</v>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Shape Rating per Item</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>-0.5845436001979822</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.354957084900288</v>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>-0.5853536730184871</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.3190391096461981</v>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>-0.5861067780271645</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.8678436241988725</v>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Number of Items</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>-0.5908457213758874</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.6403202739385232</v>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>-0.602063026742502</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.4753043693703725</v>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute KS Statistic of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>-0.6119353915956469</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.01529137342014261</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Number of Ratings Density</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>-0.6326315501392918</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.8733200788597514</v>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Model Name_FOCF Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>-0.6478406047989536</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.6358085297092636</v>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Number of Items Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>-0.6576078358038223</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.4336609420065534</v>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>-0.6584931898915443</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.6531339687069373</v>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>-0.6595995690745033</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.2580438937788718</v>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Number of Ratings Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>-0.6604718822859272</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.7235146026452947</v>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Rating per Item Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>-0.6715037902725163</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.6314697910348356</v>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>-0.6771862976699636</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.2660226575615631</v>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Density</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>-0.6819215566101406</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.5274478024622042</v>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>-0.6839216415214115</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.2448743122675718</v>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Number of Users</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>-0.6899741254694794</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.4381111048467169</v>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Number of Items Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>-0.7270503507318402</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.4386477379948229</v>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Mean Rating</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>-0.7382980681328419</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.9601694109981795</v>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>-0.7704992242023707</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.4725743585824524</v>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Shape Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>-0.7789693287762787</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.2743738606004753</v>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>-0.7819890182300229</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.2072257635016624</v>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Overestimation Unfairness of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>-0.7873767527583319</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.2370673902087417</v>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>-0.7891261165012937</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.4085703351504446</v>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Density Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.8814277093456733</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.641297241844542</v>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Gini User</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>-0.904984474986855</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.4959367626631352</v>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Gini Item Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>-0.9217930613940053</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.4658037673436264</v>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>-0.9223553893666256</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.6053515910934917</v>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>-0.9232374082503261</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.07827725368736178</v>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>-0.9718081935804541</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.04382957158818455</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>-1.002803956902399</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.02436922082095279</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>-1.009288511398717</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.5293765282656504</v>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>-1.02710245246465</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.07554391356009944</v>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Number of Items Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>-1.046127286017151</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.6905478929331682</v>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Number of Ratings Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-1.075844158972048</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.07425400118540924</v>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Shape Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>-1.07783037068381</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.1102050929950419</v>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>-1.081087569842967</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.08571842627051607</v>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Rating per Item</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>-1.14742636328418</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.02262626242275392</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>-1.232385660520727</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.4767852727981348</v>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Gini Item</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>-1.280641809816905</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.3624477894334904</v>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Gini Item</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>-1.298512217359475</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.3980959898986983</v>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Number of Items</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>-1.307093721468283</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.6578286959196982</v>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>-1.310946577093577</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.1768232759558504</v>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Shape</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-1.364071321111171</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.07897397589913292</v>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Number of Ratings Gini Item</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>-1.37946341204474</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.76628102896853</v>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Skewness of Long Tail Items Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-1.453387047997711</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.4986150053589717</v>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>-1.49298021112459</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.3785322915100752</v>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Gini Item Gini User</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>-1.596373185383717</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.5876889526671123</v>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>-1.604440550307195</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.3797723835584365</v>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Sensitive Feature_Age Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>-1.620822664907934</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.6782749657354621</v>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>-1.620822665839976</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.6782749655371505</v>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Value Unfairness of sensitive attribute Gini User</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>-1.77101507734102</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.2921975137801244</v>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>-1.790565277417058</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.05618064013940056</v>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Overestimation Unfairness of sensitive attribute Gini Item</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>-1.799871880184877</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.1349677346031293</v>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>-1.79989629949886</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.2660695783440062</v>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>KS Statistic of sensitive attribute</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>-1.828312091949983</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.08205209624070237</v>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Shape Density</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-1.962901227004747</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.2714028994454047</v>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-1.963276506428592</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.2665159894406412</v>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Gini User Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-2.033006030356822</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.6799753789881358</v>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Rating per User Gini Item</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-2.076657807417522</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.3196548756110756</v>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Number of Items Density</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-2.084508699502168</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.1315888686796705</v>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Density</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-2.093956442381052</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.03535572585155067</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Number of Items Mean Rating</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>-2.095214531813848</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.7190526867607794</v>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Density Rating per Item</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>-2.147206946832201</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.5017665091980295</v>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Density Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>-2.229253114168633</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.4008817706509359</v>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>-2.231998051791464</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.2348971390460166</v>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Gini Item Mean Rating</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>-2.262490042478497</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.8515279823652945</v>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Gini Item</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>-2.305603926424989</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.0009112625661986034</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Gini Item Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>-2.381493792794084</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.1891189997822317</v>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Shape Gini User</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-2.473661608252104</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.6031998156139019</v>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Number of Items Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>-2.475521485638365</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.4142914899200578</v>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Number of Ratings Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>-2.506298768227359</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.01359257642395657</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Mean Rating Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>-2.72043534249443</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.7739275919000923</v>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias Mean Rating</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>-2.81231706281934</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.4518234281689082</v>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Gini User Skewness of Long Tail Items</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>-2.820742185094699</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.1549207062119347</v>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Density Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>-2.869314445289345</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.2793786099424624</v>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Rating per User Mean Rating</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>-2.980500945744005</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.653805386156129</v>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Differential Fairness of sensitive attribute Number of Ratings</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>-3.002541059500264</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.005306660102054828</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Density Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>-3.321629966787058</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.2133964845597162</v>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>-3.445183445423114</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.04601827770924598</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Gini User Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>-3.705872054506773</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.2507185609753882</v>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Density Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>-3.797476716562423</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.340515921865585</v>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>-4.190892119024935</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.05661160723208877</v>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Gini Item Difference between Sensitive Attribute Percentage</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>-4.396536893050538</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.2247577743219046</v>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Generalized Cross Entropy</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>-4.54268634187992</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.1082740627933774</v>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Density Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>-4.622720809900396</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.2461405888191047</v>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Shape Mean Rating</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>-6.657639544102389</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.4896431090637905</v>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Rating per User Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>-6.991075709480628</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.06653179992914234</v>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Number of Users Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>-7.634253064335091</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.4769349923699358</v>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Density Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>-8.178236978272549</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.2865216878102607</v>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Number of Ratings Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>-8.606892355075537</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.4534900559057535</v>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-9.153462950756998</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.2931995421546027</v>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Shape Gini Item</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>-9.257857054387419</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.04890447584038717</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Gini User Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>-9.530644402053349</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.326033007095578</v>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Number of Ratings Gini User</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>-10.65661886083971</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.2723506529809441</v>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Gini User Mean Rating</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>-11.0896058706873</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.1456577541452294</v>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>-11.63929502441971</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.2841827372840538</v>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Number of Ratings Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>-11.74398679491151</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.9090433700645812</v>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Number of Ratings Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>-12.08524653832004</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.9064081651304159</v>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Number of Ratings Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>-12.10312211711826</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.9062731874033751</v>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Rating per Item Model Name_PFCN_MLP</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>-14.86176379477773</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.007366474081947591</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Rating per Item Model Name_NFCF</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>-14.91324044372641</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.00714538031792771</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Rating per Item Model Name_FOCF</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>-15.48564414522385</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.005294114051221258</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Rating per Item Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>-16.39754843948266</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.004253985749989387</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Number of Ratings Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>-17.77917293055754</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.9056817791199632</v>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Shape Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>-18.21910574553747</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.0009587505350812872</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Number of Ratings Dataset_BX</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>-19.54609770407205</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.9180110073686307</v>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Number of Ratings Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>-20.71017503566475</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.8900886016194326</v>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Number of Ratings Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>-21.86515854352348</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.9082179528861145</v>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Rating per Item Sensitive Feature_Gender</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>-22.54643882033989</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.006856514843825504</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Rating per Item Sensitive Feature_Age</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>-22.71420956473568</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.006250621009549357</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Number of Users Rating per Item</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>-30.68280383267484</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.6663202026143362</v>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Number of Ratings</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>-36.54806397638015</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.9072395444200376</v>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Rating per Item Dataset_ml1m</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>-39.44148099222545</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.008090769895726158</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Rating per Item</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>-46.33036754443593</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.006473740617297582</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Number of Items Shape</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>-50.60475735671963</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.1701561548293642</v>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>hit@5</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Number of Items Rating per Item</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>-289.3550543138488</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.5672068269810655</v>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
         <is>
           <t>hit@5</t>
         </is>
